--- a/data/trans_orig/P57B1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido deprimido en 2023</t>
+          <t>Población según se ha sentido deprimido en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28474</t>
+          <t>29090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49650</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48569</t>
+          <t>48228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44937</t>
+          <t>45772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65685</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78123</t>
+          <t>75815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109032</t>
+          <t>105606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>144280</t>
+          <t>141942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>190247</t>
+          <t>189000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207548</t>
+          <t>206887</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>244297</t>
+          <t>244832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>361397</t>
+          <t>361917</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>418672</t>
+          <t>421490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>385537</t>
+          <t>388912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>436162</t>
+          <t>439482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>354717</t>
+          <t>352484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>392403</t>
+          <t>391726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>753429</t>
+          <t>753159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>817375</t>
+          <t>818830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,71%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25823</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46283</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>68730</t>
+          <t>67762</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64390</t>
+          <t>66308</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72479</t>
+          <t>72620</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100109</t>
+          <t>99117</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90324</t>
+          <t>87778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157607</t>
+          <t>158216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>155766</t>
+          <t>141842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>388794</t>
+          <t>390311</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329763</t>
+          <t>330030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382748</t>
+          <t>381374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>437160</t>
+          <t>389283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>753177</t>
+          <t>750208</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>719824</t>
+          <t>720389</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>993125</t>
+          <t>1018803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>451203</t>
+          <t>453002</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>506036</t>
+          <t>507377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1184144</t>
+          <t>1189477</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1587297</t>
+          <t>1650165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21757</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>21978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16703</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39177</t>
+          <t>37345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24916</t>
+          <t>25124</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48350</t>
+          <t>48387</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71943</t>
+          <t>70309</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55022</t>
+          <t>55734</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107524</t>
+          <t>108920</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163278</t>
+          <t>163559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217509</t>
+          <t>215563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>257834</t>
+          <t>253658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>646512</t>
+          <t>680993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>443311</t>
+          <t>442634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>935171</t>
+          <t>967244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>437393</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>493068</t>
+          <t>491392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>246842</t>
+          <t>213272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>591834</t>
+          <t>596435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>628076</t>
+          <t>594932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1066020</t>
+          <t>1065986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12591</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29829</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39475</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65823</t>
+          <t>64490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46086</t>
+          <t>46734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73592</t>
+          <t>73570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>69922</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>104315</t>
+          <t>106950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126098</t>
+          <t>125968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>172357</t>
+          <t>169050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>264230</t>
+          <t>265101</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>324100</t>
+          <t>322879</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>301287</t>
+          <t>304604</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>421251</t>
+          <t>423987</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>589711</t>
+          <t>605432</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>719998</t>
+          <t>720186</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522276</t>
+          <t>522603</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>584463</t>
+          <t>585693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>545185</t>
+          <t>543000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>702888</t>
+          <t>688479</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1094907</t>
+          <t>1090984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1255876</t>
+          <t>1230424</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>53927</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88433</t>
+          <t>89409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78644</t>
+          <t>79609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>118046</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>141203</t>
+          <t>140650</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>195298</t>
+          <t>190786</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>141458</t>
+          <t>137460</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206825</t>
+          <t>206484</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226465</t>
+          <t>232016</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>311066</t>
+          <t>312613</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>400313</t>
+          <t>392413</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>505811</t>
+          <t>504889</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>743946</t>
+          <t>729565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1034568</t>
+          <t>1037985</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1223061</t>
+          <t>1217813</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1793914</t>
+          <t>1736718</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2086998</t>
+          <t>2085068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2860748</t>
+          <t>2779459</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,13%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2152979</t>
+          <t>2148417</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2523504</t>
+          <t>2526586</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1559751</t>
+          <t>1606274</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2039803</t>
+          <t>2042571</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3780572</t>
+          <t>3819303</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4441594</t>
+          <t>4456540</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12251</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29090</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>31524</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>43823</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>33243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51030</t>
+          <t>56772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>36032</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48228</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55233</t>
+          <t>61263</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45772</t>
+          <t>50043</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66010</t>
+          <t>72803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91265</t>
+          <t>100755</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75815</t>
+          <t>84591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105606</t>
+          <t>119114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>183076</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141942</t>
+          <t>160537</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>189000</t>
+          <t>208013</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225024</t>
+          <t>243295</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>206887</t>
+          <t>222562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>244832</t>
+          <t>265922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>389818</t>
+          <t>426371</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>361917</t>
+          <t>396368</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>421490</t>
+          <t>457409</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>413531</t>
+          <t>444904</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>388912</t>
+          <t>418781</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439482</t>
+          <t>469956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>372745</t>
+          <t>402365</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>352484</t>
+          <t>379776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>391726</t>
+          <t>425182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>786276</t>
+          <t>847269</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>753159</t>
+          <t>811948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>818830</t>
+          <t>880847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>633124</t>
+          <t>688356</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>633124</t>
+          <t>688356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>633124</t>
+          <t>688356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>672622</t>
+          <t>729862</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672622</t>
+          <t>729862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>672622</t>
+          <t>729862</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1305746</t>
+          <t>1418218</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1305746</t>
+          <t>1418218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1305746</t>
+          <t>1418218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>20969</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27331</t>
+          <t>30895</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34405</t>
+          <t>39631</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46888</t>
+          <t>52947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>60600</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>67762</t>
+          <t>76966</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47192</t>
+          <t>51023</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>40078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66308</t>
+          <t>66362</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>97862</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72620</t>
+          <t>82741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99117</t>
+          <t>114453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>132702</t>
+          <t>148884</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87778</t>
+          <t>130527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>174098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>297331</t>
+          <t>341036</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141842</t>
+          <t>310710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>390311</t>
+          <t>378873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>356027</t>
+          <t>398541</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330030</t>
+          <t>368303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>381374</t>
+          <t>425928</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>653358</t>
+          <t>739577</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>389283</t>
+          <t>698971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>750208</t>
+          <t>785409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>828512</t>
+          <t>633433</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>720389</t>
+          <t>596202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1018803</t>
+          <t>666298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>479944</t>
+          <t>532409</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>453002</t>
+          <t>502124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>507377</t>
+          <t>562011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1308456</t>
+          <t>1165843</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1189477</t>
+          <t>1116096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1650165</t>
+          <t>1210362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>57,23%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1190649</t>
+          <t>1046461</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1190649</t>
+          <t>1046461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1190649</t>
+          <t>1046461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>955887</t>
+          <t>1068443</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>955887</t>
+          <t>1068443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>955887</t>
+          <t>1068443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2146536</t>
+          <t>2114904</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2146536</t>
+          <t>2114904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2146536</t>
+          <t>2114904</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>26435</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16630</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37345</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>42098</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25124</t>
+          <t>30343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48387</t>
+          <t>57990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50198</t>
+          <t>55560</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>43306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>71293</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>85255</t>
+          <t>97658</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55734</t>
+          <t>80273</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>108920</t>
+          <t>118082</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>189447</t>
+          <t>212827</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163559</t>
+          <t>187493</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>215563</t>
+          <t>241238</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>414899</t>
+          <t>247219</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253658</t>
+          <t>222353</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>680993</t>
+          <t>273991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>604346</t>
+          <t>460047</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>442634</t>
+          <t>420069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>967244</t>
+          <t>494680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>465019</t>
+          <t>532043</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>434434</t>
+          <t>503270</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>491392</t>
+          <t>559397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>452947</t>
+          <t>492735</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>213272</t>
+          <t>464657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>596435</t>
+          <t>517226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>917967</t>
+          <t>1024778</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>594932</t>
+          <t>984095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1065986</t>
+          <t>1067022</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,23%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>702475</t>
+          <t>800828</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>702475</t>
+          <t>800828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>702475</t>
+          <t>800828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931528</t>
+          <t>810353</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931528</t>
+          <t>810353</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931528</t>
+          <t>810353</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1634003</t>
+          <t>1611181</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1634003</t>
+          <t>1611181</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1634003</t>
+          <t>1611181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>13517</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31100</t>
+          <t>36202</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22355</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41004</t>
+          <t>47050</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>50554</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39859</t>
+          <t>45148</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>71151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>59057</t>
+          <t>66633</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46734</t>
+          <t>53181</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73570</t>
+          <t>84215</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>87785</t>
+          <t>96763</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69922</t>
+          <t>81895</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106950</t>
+          <t>115034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>146842</t>
+          <t>163396</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>125968</t>
+          <t>143431</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169050</t>
+          <t>186771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>291529</t>
+          <t>320402</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>265101</t>
+          <t>288122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>322879</t>
+          <t>350500</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>383636</t>
+          <t>424086</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>304604</t>
+          <t>396369</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>423987</t>
+          <t>452895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>675165</t>
+          <t>744488</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>605432</t>
+          <t>701964</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>720186</t>
+          <t>786457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>554769</t>
+          <t>580121</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>522603</t>
+          <t>546586</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>585693</t>
+          <t>616984</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>589300</t>
+          <t>558752</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>543000</t>
+          <t>523790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>688479</t>
+          <t>588294</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1144068</t>
+          <t>1138873</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1090984</t>
+          <t>1095698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1230424</t>
+          <t>1183916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>56,27%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>924810</t>
+          <t>988149</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>924810</t>
+          <t>988149</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>924810</t>
+          <t>988149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1091821</t>
+          <t>1115803</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091821</t>
+          <t>1115803</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091821</t>
+          <t>1115803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2016630</t>
+          <t>2103952</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2016630</t>
+          <t>2103952</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2016630</t>
+          <t>2103952</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>76707</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>60583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>89409</t>
+          <t>96189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>98610</t>
+          <t>113610</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79609</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118046</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>167395</t>
+          <t>190317</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>140650</t>
+          <t>166970</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>190786</t>
+          <t>216207</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>177339</t>
+          <t>199246</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137460</t>
+          <t>175465</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>206484</t>
+          <t>227486</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>278726</t>
+          <t>311448</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>232016</t>
+          <t>283509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>312613</t>
+          <t>341646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>456065</t>
+          <t>510694</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>392413</t>
+          <t>474432</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>504889</t>
+          <t>553907</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>943101</t>
+          <t>1057340</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729565</t>
+          <t>1000549</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1037985</t>
+          <t>1119213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1379587</t>
+          <t>1313142</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1217813</t>
+          <t>1266341</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1736718</t>
+          <t>1371876</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2322688</t>
+          <t>2370482</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2085068</t>
+          <t>2291310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2779459</t>
+          <t>2453396</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2261832</t>
+          <t>2190502</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2148417</t>
+          <t>2126657</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2526586</t>
+          <t>2252364</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1894936</t>
+          <t>1986260</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1606274</t>
+          <t>1933503</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2042571</t>
+          <t>2038487</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4156768</t>
+          <t>4176762</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3819303</t>
+          <t>4089823</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4456540</t>
+          <t>4256625</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3451058</t>
+          <t>3523794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3651858</t>
+          <t>3724460</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7102916</t>
+          <t>7248254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
